--- a/data/trans_camb/IP16B03-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16B03-Clase-trans_camb.xlsx
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,37</t>
+          <t>0,0; 83,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 501,34</t>
+          <t>0,0; 501,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 0,0</t>
+          <t>-51,48; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-75,0; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,24</t>
+          <t>0,0; 46,44</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,83</t>
+          <t>0,0; 39,29</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 9,57</t>
+          <t>-20,1; 9,42</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-17,12; 12,4</t>
+          <t>-17,14; 9,76</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 0,0</t>
+          <t>-51,48; 0,0</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-75,0; 0,0</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,33</t>
+          <t>0,0; 86,84</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,0</t>
+          <t>0,0; 64,71</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-18,21; 10,53</t>
+          <t>-22,13; 10,38</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 14,35</t>
+          <t>-17,22; 10,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B03-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16B03-Clase-trans_camb.xlsx
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,38</t>
+          <t>0,0; 77,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 501,38</t>
+          <t>0,0; 309,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 0,0</t>
+          <t>-44,32; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1577,22 +1577,22 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,44</t>
+          <t>0,0; 46,5</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,29</t>
+          <t>0,0; 39,23</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-20,1; 9,42</t>
+          <t>-19,44; 9,48</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 9,76</t>
+          <t>-17,15; 9,67</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 0,0</t>
+          <t>-44,32; 0,0</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1653,22 +1653,22 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0,0; 86,84</t>
+          <t>0,0; 86,98</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,71</t>
+          <t>0,0; 64,55</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-22,13; 10,38</t>
+          <t>-20,85; 10,43</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 10,73</t>
+          <t>-17,16; 10,67</t>
         </is>
       </c>
     </row>
